--- a/TIMES-NZ/v303/VT_TIMESNZ_IND.xlsx
+++ b/TIMES-NZ/v303/VT_TIMESNZ_IND.xlsx
@@ -5551,7 +5551,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>NGA</t>
+          <t>FSTKNGA</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -5595,7 +5595,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>COA</t>
+          <t>FSTKCOA</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -19495,7 +19495,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>NGA</t>
+          <t>FSTKNGA</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
@@ -24956,7 +24956,7 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>COA</t>
+          <t>FSTKCOA</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
@@ -26056,7 +26056,7 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>NGA</t>
+          <t>FSTKNGA</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
@@ -31212,7 +31212,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -31492,149 +31492,134 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>FTE_FSTKNGA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>GW</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>FTE_INDOSWOD</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>PRE</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>PJ</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>GW</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>FTE_FSTKCOA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>GW</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>IndustryFuelProcessParameters</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
+      <c r="B18" s="1" t="inlineStr">
         <is>
           <t>Sets parameters for industry fuel delivery processes (mostly delivery costs)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>~FI_T</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Comm-OUT</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Comm-IN</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>TechName</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>LIFE</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>EFF</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VAROM</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>INDELC</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>ELCDD</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>FTE_INDELC</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>~FI_T</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>INDFOL</t>
+          <t>Comm-OUT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FOL</t>
+          <t>Comm-IN</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>FTE_INDFOL</t>
+          <t>TechName</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>LIFE</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>EFF</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>VAROM</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>INDBIG</t>
+          <t>INDELC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BIG</t>
+          <t>ELCDD</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FTE_INDBIG</t>
+          <t>FTE_INDELC</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -31651,17 +31636,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>INDNGA</t>
+          <t>INDFOL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NGA</t>
+          <t>FOL</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>FTE_INDNGA</t>
+          <t>FTE_INDFOL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -31676,24 +31661,24 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.746</t>
+          <t>0.92</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>INDDSL</t>
+          <t>INDBIG</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DSL</t>
+          <t>BIG</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>FTE_INDDSL</t>
+          <t>FTE_INDBIG</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -31704,28 +31689,23 @@
       <c r="E23" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>0.92</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>INDPET</t>
+          <t>INDNGA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PET</t>
+          <t>NGADD</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>FTE_INDPET</t>
+          <t>FTE_INDNGA</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -31736,28 +31716,23 @@
       <c r="E24" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>0.92</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>INDCOA</t>
+          <t>INDDSL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>COA</t>
+          <t>DSL</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>FTE_INDCOA</t>
+          <t>FTE_INDDSL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -31768,23 +31743,28 @@
       <c r="E25" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>0.92</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>INDGEO</t>
+          <t>INDPET</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GEO</t>
+          <t>PET</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>FTE_INDGEO</t>
+          <t>FTE_INDPET</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -31795,23 +31775,28 @@
       <c r="E26" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>0.92</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>INDLPG</t>
+          <t>INDCOA</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LPG</t>
+          <t>COA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>FTE_INDLPG</t>
+          <t>FTE_INDCOA</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -31828,17 +31813,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>INDWOD</t>
+          <t>INDGEO</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>WOD</t>
+          <t>GEO</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>FTE_INDWOD</t>
+          <t>FTE_INDGEO</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -31855,25 +31840,133 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>INDLPG</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>LPG</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>FTE_INDLPG</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>INDWOD</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>WOD</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>FTE_INDWOD</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>FSTKNGA</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>NGADD</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>FTE_FSTKNGA</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>INDOSWOD</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>OSWOD</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>FTE_INDOSWOD</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>FSTKCOA</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>COA</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>FTE_FSTKCOA</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
         <is>
           <t>1</t>
         </is>
